--- a/admin/assets/BOMB-HR-每月班表範例.xlsx
+++ b/admin/assets/BOMB-HR-每月班表範例.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每月班表" sheetId="1" r:id="R6ceb5d6bf6314e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每月班表" sheetId="1" r:id="R7d2cde4027084f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="假別代號設定" sheetId="2" r:id="R2f9b4caa7e044f38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +17,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -55,8 +56,18 @@
       <x:color rgb="FF92400E"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0F172A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF3730A3"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,8 +104,28 @@
         <x:fgColor rgb="FFFEF3C7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4F46E5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF312E81"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF2FF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -138,11 +169,63 @@
         <x:color rgb="FF93C5FD"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFA5B4FC"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -197,10 +280,160 @@
     <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="6">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9F1239"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFE4E6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1D4ED8"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDBEAFE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF334155"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2E8F0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFBE185D"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE7F3"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -490,7 +723,7 @@
       </x:c>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9" t="str">
-        <x:v>填寫方式：日期欄輸入「1」代表依該員工班別上班；輸入「休」或留白代表未排班。假別不需手填，核准後系統會自動標記。</x:v>
+        <x:v>填寫方式：日期欄請由下拉選單選擇「1、休、年、旅、喪、婚、病」。若要新增假別，請至「假別代號設定」工作表新增；核准後系統仍會自動比對並標記。</x:v>
       </x:c>
       <x:c r="E2" s="9"/>
       <x:c r="F2" s="9"/>
@@ -2096,11 +2329,289 @@
     <x:mergeCell ref="AJ15:AL15"/>
     <x:mergeCell ref="A17:AL17"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="E5:AI14">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="休"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="年"/>
+    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="旅"/>
+    <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="喪"/>
+    <x:cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="婚"/>
+    <x:cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="病"/>
+  </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="E5:AI14">
-      <x:formula1>"1,休"</x:formula1>
+      <x:formula1>'假別代號設定'!$A$2:$A$50</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="33" t="str">
+        <x:v>排班代號</x:v>
+      </x:c>
+      <x:c r="B1" s="33" t="str">
+        <x:v>顯示名稱</x:v>
+      </x:c>
+      <x:c r="D1" s="40" t="str">
+        <x:v>自訂方式</x:v>
+      </x:c>
+      <x:c r="E1" s="40"/>
+      <x:c r="F1" s="40"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="37" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="36" t="str">
+        <x:v>上班</x:v>
+      </x:c>
+      <x:c r="D2" s="61" t="str">
+        <x:v>請從第 9 列開始新增代號與名稱。
+月班表的下拉選單會自動讀取 A2:A50，不需重新製作表格。
+代號建議使用 1～2 個中文字，避免重複。</x:v>
+      </x:c>
+      <x:c r="E2" s="62"/>
+      <x:c r="F2" s="63"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="37" t="str">
+        <x:v>休</x:v>
+      </x:c>
+      <x:c r="B3" s="36" t="str">
+        <x:v>休假／未排班</x:v>
+      </x:c>
+      <x:c r="D3" s="64"/>
+      <x:c r="E3" s="65"/>
+      <x:c r="F3" s="66"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="37" t="str">
+        <x:v>年</x:v>
+      </x:c>
+      <x:c r="B4" s="36" t="str">
+        <x:v>年假</x:v>
+      </x:c>
+      <x:c r="D4" s="67"/>
+      <x:c r="E4" s="68"/>
+      <x:c r="F4" s="69"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="37" t="str">
+        <x:v>旅</x:v>
+      </x:c>
+      <x:c r="B5" s="36" t="str">
+        <x:v>旅遊假</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="37" t="str">
+        <x:v>喪</x:v>
+      </x:c>
+      <x:c r="B6" s="36" t="str">
+        <x:v>喪假</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="37" t="str">
+        <x:v>婚</x:v>
+      </x:c>
+      <x:c r="B7" s="36" t="str">
+        <x:v>婚假</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="37" t="str">
+        <x:v>病</x:v>
+      </x:c>
+      <x:c r="B8" s="36" t="str">
+        <x:v>病假</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="37"/>
+      <x:c r="B9" s="36"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="37"/>
+      <x:c r="B10" s="36"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="37"/>
+      <x:c r="B11" s="36"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="37"/>
+      <x:c r="B12" s="36"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="37"/>
+      <x:c r="B13" s="36"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="37"/>
+      <x:c r="B14" s="36"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="37"/>
+      <x:c r="B15" s="36"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="37"/>
+      <x:c r="B16" s="36"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="37"/>
+      <x:c r="B17" s="36"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="37"/>
+      <x:c r="B18" s="36"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="37"/>
+      <x:c r="B19" s="36"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="37"/>
+      <x:c r="B20" s="36"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="37"/>
+      <x:c r="B21" s="36"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="37"/>
+      <x:c r="B22" s="36"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="37"/>
+      <x:c r="B23" s="36"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="37"/>
+      <x:c r="B24" s="36"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="37"/>
+      <x:c r="B25" s="36"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="37"/>
+      <x:c r="B26" s="36"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="37"/>
+      <x:c r="B27" s="36"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="37"/>
+      <x:c r="B28" s="36"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="37"/>
+      <x:c r="B29" s="36"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="37"/>
+      <x:c r="B30" s="36"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="37"/>
+      <x:c r="B31" s="36"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="37"/>
+      <x:c r="B32" s="36"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="37"/>
+      <x:c r="B33" s="36"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="37"/>
+      <x:c r="B34" s="36"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="37"/>
+      <x:c r="B35" s="36"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="37"/>
+      <x:c r="B36" s="36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="37"/>
+      <x:c r="B37" s="36"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="37"/>
+      <x:c r="B38" s="36"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="37"/>
+      <x:c r="B39" s="36"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="37"/>
+      <x:c r="B40" s="36"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="37"/>
+      <x:c r="B41" s="36"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="37"/>
+      <x:c r="B42" s="36"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="37"/>
+      <x:c r="B43" s="36"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="37"/>
+      <x:c r="B44" s="36"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="37"/>
+      <x:c r="B45" s="36"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="37"/>
+      <x:c r="B46" s="36"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="37"/>
+      <x:c r="B47" s="36"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="37"/>
+      <x:c r="B48" s="36"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="37"/>
+      <x:c r="B49" s="36"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="37"/>
+      <x:c r="B50" s="36"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D1:F1"/>
+    <x:mergeCell ref="D2:F4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>